--- a/atop-20260419095608/atop_20260419.xlsx
+++ b/atop-20260419095608/atop_20260419.xlsx
@@ -65021,11 +65021,23 @@
       <c r="B21">
         <v>2.9133333333333336</v>
       </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
         <v>29</v>
       </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
       <c r="C22">
         <v>459.1166666666667</v>
       </c>
@@ -65043,6 +65055,15 @@
       <c r="B23">
         <v>2.83</v>
       </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
@@ -65051,6 +65072,15 @@
       <c r="B24">
         <v>2.796666666666667</v>
       </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
@@ -65059,6 +65089,15 @@
       <c r="B25">
         <v>3.203333333333333</v>
       </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
@@ -65067,6 +65106,15 @@
       <c r="B26">
         <v>3.1433333333333335</v>
       </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
@@ -65075,6 +65123,15 @@
       <c r="B27">
         <v>3.6266666666666665</v>
       </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
@@ -65083,6 +65140,15 @@
       <c r="B28">
         <v>3.6266666666666665</v>
       </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
@@ -65091,6 +65157,15 @@
       <c r="B29">
         <v>3.5866666666666664</v>
       </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
@@ -65099,6 +65174,15 @@
       <c r="B30">
         <v>3.5533333333333332</v>
       </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
@@ -65107,6 +65191,15 @@
       <c r="B31">
         <v>3.5566666666666666</v>
       </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
@@ -65115,6 +65208,15 @@
       <c r="B32">
         <v>3.4966666666666666</v>
       </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
@@ -65123,6 +65225,15 @@
       <c r="B33">
         <v>3.5</v>
       </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
@@ -65131,6 +65242,15 @@
       <c r="B34">
         <v>3.48</v>
       </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
@@ -65139,6 +65259,15 @@
       <c r="B35">
         <v>3.48</v>
       </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
@@ -65147,6 +65276,15 @@
       <c r="B36">
         <v>3.4633333333333334</v>
       </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
@@ -65155,6 +65293,15 @@
       <c r="B37">
         <v>3.5533333333333332</v>
       </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
@@ -65163,6 +65310,15 @@
       <c r="B38">
         <v>3.4833333333333334</v>
       </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
@@ -65171,6 +65327,15 @@
       <c r="B39">
         <v>3.4833333333333334</v>
       </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
@@ -65179,6 +65344,15 @@
       <c r="B40">
         <v>3.4566666666666666</v>
       </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
@@ -65187,6 +65361,15 @@
       <c r="B41">
         <v>3.47</v>
       </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
@@ -65195,6 +65378,15 @@
       <c r="B42">
         <v>3.3566666666666665</v>
       </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
@@ -65203,6 +65395,15 @@
       <c r="B43">
         <v>3.4366666666666665</v>
       </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
@@ -65211,6 +65412,15 @@
       <c r="B44">
         <v>3.3466666666666667</v>
       </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
@@ -65219,6 +65429,15 @@
       <c r="B45">
         <v>3.526666666666667</v>
       </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
@@ -65227,6 +65446,15 @@
       <c r="B46">
         <v>3.57</v>
       </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+      <c r="D46">
+        <v>0</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
@@ -65235,6 +65463,15 @@
       <c r="B47">
         <v>3.5033333333333334</v>
       </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
@@ -65243,6 +65480,15 @@
       <c r="B48">
         <v>3.3466666666666667</v>
       </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
@@ -65251,6 +65497,15 @@
       <c r="B49">
         <v>3.3033333333333332</v>
       </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
@@ -65259,6 +65514,15 @@
       <c r="B50">
         <v>3.3833333333333333</v>
       </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
@@ -65267,6 +65531,15 @@
       <c r="B51">
         <v>3.2266666666666666</v>
       </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
@@ -65275,6 +65548,15 @@
       <c r="B52">
         <v>2.98</v>
       </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
+      <c r="D52">
+        <v>0</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
@@ -65283,6 +65565,15 @@
       <c r="B53">
         <v>3.17</v>
       </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
+      <c r="D53">
+        <v>0</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
@@ -65291,6 +65582,15 @@
       <c r="B54">
         <v>3.026666666666667</v>
       </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
@@ -65299,6 +65599,15 @@
       <c r="B55">
         <v>3.26</v>
       </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
@@ -65307,6 +65616,15 @@
       <c r="B56">
         <v>3.2666666666666666</v>
       </c>
+      <c r="C56">
+        <v>0</v>
+      </c>
+      <c r="D56">
+        <v>0</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
@@ -65315,6 +65633,15 @@
       <c r="B57">
         <v>3.493333333333333</v>
       </c>
+      <c r="C57">
+        <v>0</v>
+      </c>
+      <c r="D57">
+        <v>0</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
@@ -65323,6 +65650,15 @@
       <c r="B58">
         <v>3.1333333333333333</v>
       </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
+      <c r="D58">
+        <v>0</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
@@ -65331,6 +65667,15 @@
       <c r="B59">
         <v>3.18</v>
       </c>
+      <c r="C59">
+        <v>0</v>
+      </c>
+      <c r="D59">
+        <v>0</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
@@ -65339,6 +65684,15 @@
       <c r="B60">
         <v>3.1766666666666667</v>
       </c>
+      <c r="C60">
+        <v>0</v>
+      </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
@@ -65347,6 +65701,15 @@
       <c r="B61">
         <v>3.263333333333333</v>
       </c>
+      <c r="C61">
+        <v>0</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
@@ -65355,6 +65718,15 @@
       <c r="B62">
         <v>3.223333333333333</v>
       </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
+      <c r="D62">
+        <v>0</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
@@ -65363,6 +65735,15 @@
       <c r="B63">
         <v>3.39</v>
       </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+      <c r="D63">
+        <v>0</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
@@ -65371,6 +65752,15 @@
       <c r="B64">
         <v>3.63</v>
       </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
+      <c r="D64">
+        <v>0</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
@@ -65379,6 +65769,15 @@
       <c r="B65">
         <v>3.6733333333333333</v>
       </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
+      <c r="D65">
+        <v>0</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
@@ -65387,6 +65786,15 @@
       <c r="B66">
         <v>3.35</v>
       </c>
+      <c r="C66">
+        <v>0</v>
+      </c>
+      <c r="D66">
+        <v>0</v>
+      </c>
+      <c r="E66">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
@@ -65395,6 +65803,15 @@
       <c r="B67">
         <v>3.243333333333333</v>
       </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
+      <c r="D67">
+        <v>0</v>
+      </c>
+      <c r="E67">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
@@ -65403,6 +65820,15 @@
       <c r="B68">
         <v>3.763333333333333</v>
       </c>
+      <c r="C68">
+        <v>0</v>
+      </c>
+      <c r="D68">
+        <v>0</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
@@ -65411,6 +65837,15 @@
       <c r="B69">
         <v>3.4233333333333333</v>
       </c>
+      <c r="C69">
+        <v>0</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
@@ -65419,6 +65854,15 @@
       <c r="B70">
         <v>3.36</v>
       </c>
+      <c r="C70">
+        <v>0</v>
+      </c>
+      <c r="D70">
+        <v>0</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
@@ -65427,6 +65871,15 @@
       <c r="B71">
         <v>3.44</v>
       </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+      <c r="D71">
+        <v>0</v>
+      </c>
+      <c r="E71">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
@@ -65435,6 +65888,15 @@
       <c r="B72">
         <v>3.283333333333333</v>
       </c>
+      <c r="C72">
+        <v>0</v>
+      </c>
+      <c r="D72">
+        <v>0</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
@@ -65443,6 +65905,15 @@
       <c r="B73">
         <v>3.11</v>
       </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+      <c r="D73">
+        <v>0</v>
+      </c>
+      <c r="E73">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
@@ -65451,6 +65922,15 @@
       <c r="B74">
         <v>3.07</v>
       </c>
+      <c r="C74">
+        <v>0</v>
+      </c>
+      <c r="D74">
+        <v>0</v>
+      </c>
+      <c r="E74">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
@@ -65459,6 +65939,15 @@
       <c r="B75">
         <v>3.0966666666666667</v>
       </c>
+      <c r="C75">
+        <v>0</v>
+      </c>
+      <c r="D75">
+        <v>0</v>
+      </c>
+      <c r="E75">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
@@ -65467,6 +65956,15 @@
       <c r="B76">
         <v>3.046666666666667</v>
       </c>
+      <c r="C76">
+        <v>0</v>
+      </c>
+      <c r="D76">
+        <v>0</v>
+      </c>
+      <c r="E76">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
@@ -65475,6 +65973,15 @@
       <c r="B77">
         <v>3.09</v>
       </c>
+      <c r="C77">
+        <v>0</v>
+      </c>
+      <c r="D77">
+        <v>0</v>
+      </c>
+      <c r="E77">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
@@ -65483,6 +65990,15 @@
       <c r="B78">
         <v>3.09</v>
       </c>
+      <c r="C78">
+        <v>0</v>
+      </c>
+      <c r="D78">
+        <v>0</v>
+      </c>
+      <c r="E78">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
@@ -65491,6 +66007,15 @@
       <c r="B79">
         <v>3.1033333333333335</v>
       </c>
+      <c r="C79">
+        <v>0</v>
+      </c>
+      <c r="D79">
+        <v>0</v>
+      </c>
+      <c r="E79">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
@@ -65499,6 +66024,15 @@
       <c r="B80">
         <v>3.0633333333333335</v>
       </c>
+      <c r="C80">
+        <v>0</v>
+      </c>
+      <c r="D80">
+        <v>0</v>
+      </c>
+      <c r="E80">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
@@ -65507,6 +66041,15 @@
       <c r="B81">
         <v>3.1133333333333333</v>
       </c>
+      <c r="C81">
+        <v>0</v>
+      </c>
+      <c r="D81">
+        <v>0</v>
+      </c>
+      <c r="E81">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
@@ -65515,6 +66058,15 @@
       <c r="B82">
         <v>3.0733333333333333</v>
       </c>
+      <c r="C82">
+        <v>0</v>
+      </c>
+      <c r="D82">
+        <v>0</v>
+      </c>
+      <c r="E82">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
@@ -65523,6 +66075,15 @@
       <c r="B83">
         <v>3.1166666666666667</v>
       </c>
+      <c r="C83">
+        <v>0</v>
+      </c>
+      <c r="D83">
+        <v>0</v>
+      </c>
+      <c r="E83">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
@@ -65531,6 +66092,15 @@
       <c r="B84">
         <v>3.0966666666666667</v>
       </c>
+      <c r="C84">
+        <v>0</v>
+      </c>
+      <c r="D84">
+        <v>0</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
@@ -65539,6 +66109,15 @@
       <c r="B85">
         <v>3.0866666666666664</v>
       </c>
+      <c r="C85">
+        <v>0</v>
+      </c>
+      <c r="D85">
+        <v>0</v>
+      </c>
+      <c r="E85">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
@@ -65547,6 +66126,15 @@
       <c r="B86">
         <v>3.1133333333333333</v>
       </c>
+      <c r="C86">
+        <v>0</v>
+      </c>
+      <c r="D86">
+        <v>0</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
@@ -65555,6 +66143,15 @@
       <c r="B87">
         <v>3.0766666666666667</v>
       </c>
+      <c r="C87">
+        <v>0</v>
+      </c>
+      <c r="D87">
+        <v>0</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
@@ -65563,6 +66160,15 @@
       <c r="B88">
         <v>3.11</v>
       </c>
+      <c r="C88">
+        <v>0</v>
+      </c>
+      <c r="D88">
+        <v>0</v>
+      </c>
+      <c r="E88">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
@@ -65571,6 +66177,15 @@
       <c r="B89">
         <v>3.0766666666666667</v>
       </c>
+      <c r="C89">
+        <v>0</v>
+      </c>
+      <c r="D89">
+        <v>0</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
@@ -65579,6 +66194,15 @@
       <c r="B90">
         <v>3.0366666666666666</v>
       </c>
+      <c r="C90">
+        <v>0</v>
+      </c>
+      <c r="D90">
+        <v>0</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
@@ -65587,6 +66211,15 @@
       <c r="B91">
         <v>3.0533333333333332</v>
       </c>
+      <c r="C91">
+        <v>0</v>
+      </c>
+      <c r="D91">
+        <v>0</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
@@ -65595,6 +66228,15 @@
       <c r="B92">
         <v>3.11</v>
       </c>
+      <c r="C92">
+        <v>0</v>
+      </c>
+      <c r="D92">
+        <v>0</v>
+      </c>
+      <c r="E92">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
@@ -65603,6 +66245,15 @@
       <c r="B93">
         <v>3.08</v>
       </c>
+      <c r="C93">
+        <v>0</v>
+      </c>
+      <c r="D93">
+        <v>0</v>
+      </c>
+      <c r="E93">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
@@ -65611,6 +66262,15 @@
       <c r="B94">
         <v>3.09</v>
       </c>
+      <c r="C94">
+        <v>0</v>
+      </c>
+      <c r="D94">
+        <v>0</v>
+      </c>
+      <c r="E94">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
@@ -65619,6 +66279,15 @@
       <c r="B95">
         <v>3.08</v>
       </c>
+      <c r="C95">
+        <v>0</v>
+      </c>
+      <c r="D95">
+        <v>0</v>
+      </c>
+      <c r="E95">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
@@ -65627,6 +66296,15 @@
       <c r="B96">
         <v>3.066666666666667</v>
       </c>
+      <c r="C96">
+        <v>0</v>
+      </c>
+      <c r="D96">
+        <v>0</v>
+      </c>
+      <c r="E96">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
@@ -65635,6 +66313,15 @@
       <c r="B97">
         <v>3.07</v>
       </c>
+      <c r="C97">
+        <v>0</v>
+      </c>
+      <c r="D97">
+        <v>0</v>
+      </c>
+      <c r="E97">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
@@ -65643,6 +66330,15 @@
       <c r="B98">
         <v>3.06</v>
       </c>
+      <c r="C98">
+        <v>0</v>
+      </c>
+      <c r="D98">
+        <v>0</v>
+      </c>
+      <c r="E98">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
@@ -65651,6 +66347,15 @@
       <c r="B99">
         <v>3.0766666666666667</v>
       </c>
+      <c r="C99">
+        <v>0</v>
+      </c>
+      <c r="D99">
+        <v>0</v>
+      </c>
+      <c r="E99">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
@@ -65659,6 +66364,15 @@
       <c r="B100">
         <v>3.07</v>
       </c>
+      <c r="C100">
+        <v>0</v>
+      </c>
+      <c r="D100">
+        <v>0</v>
+      </c>
+      <c r="E100">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
@@ -65667,6 +66381,15 @@
       <c r="B101">
         <v>3.08</v>
       </c>
+      <c r="C101">
+        <v>0</v>
+      </c>
+      <c r="D101">
+        <v>0</v>
+      </c>
+      <c r="E101">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
@@ -65675,6 +66398,15 @@
       <c r="B102">
         <v>3.0766666666666667</v>
       </c>
+      <c r="C102">
+        <v>0</v>
+      </c>
+      <c r="D102">
+        <v>0</v>
+      </c>
+      <c r="E102">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
@@ -65683,6 +66415,15 @@
       <c r="B103">
         <v>3.066666666666667</v>
       </c>
+      <c r="C103">
+        <v>0</v>
+      </c>
+      <c r="D103">
+        <v>0</v>
+      </c>
+      <c r="E103">
+        <v>0</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
@@ -65691,6 +66432,15 @@
       <c r="B104">
         <v>3.0633333333333335</v>
       </c>
+      <c r="C104">
+        <v>0</v>
+      </c>
+      <c r="D104">
+        <v>0</v>
+      </c>
+      <c r="E104">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
@@ -65699,6 +66449,15 @@
       <c r="B105">
         <v>3.09</v>
       </c>
+      <c r="C105">
+        <v>0</v>
+      </c>
+      <c r="D105">
+        <v>0</v>
+      </c>
+      <c r="E105">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
@@ -65707,6 +66466,15 @@
       <c r="B106">
         <v>3.11</v>
       </c>
+      <c r="C106">
+        <v>0</v>
+      </c>
+      <c r="D106">
+        <v>0</v>
+      </c>
+      <c r="E106">
+        <v>0</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
@@ -65715,6 +66483,15 @@
       <c r="B107">
         <v>3.0733333333333333</v>
       </c>
+      <c r="C107">
+        <v>0</v>
+      </c>
+      <c r="D107">
+        <v>0</v>
+      </c>
+      <c r="E107">
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
@@ -65723,6 +66500,15 @@
       <c r="B108">
         <v>3.066666666666667</v>
       </c>
+      <c r="C108">
+        <v>0</v>
+      </c>
+      <c r="D108">
+        <v>0</v>
+      </c>
+      <c r="E108">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
@@ -65731,6 +66517,15 @@
       <c r="B109">
         <v>3.0833333333333335</v>
       </c>
+      <c r="C109">
+        <v>0</v>
+      </c>
+      <c r="D109">
+        <v>0</v>
+      </c>
+      <c r="E109">
+        <v>0</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
@@ -65739,6 +66534,15 @@
       <c r="B110">
         <v>3.04</v>
       </c>
+      <c r="C110">
+        <v>0</v>
+      </c>
+      <c r="D110">
+        <v>0</v>
+      </c>
+      <c r="E110">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
@@ -65747,6 +66551,15 @@
       <c r="B111">
         <v>3.08</v>
       </c>
+      <c r="C111">
+        <v>0</v>
+      </c>
+      <c r="D111">
+        <v>0</v>
+      </c>
+      <c r="E111">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
@@ -65755,6 +66568,15 @@
       <c r="B112">
         <v>3.0866666666666664</v>
       </c>
+      <c r="C112">
+        <v>0</v>
+      </c>
+      <c r="D112">
+        <v>0</v>
+      </c>
+      <c r="E112">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
@@ -65763,6 +66585,15 @@
       <c r="B113">
         <v>3.0833333333333335</v>
       </c>
+      <c r="C113">
+        <v>0</v>
+      </c>
+      <c r="D113">
+        <v>0</v>
+      </c>
+      <c r="E113">
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
@@ -65771,6 +66602,15 @@
       <c r="B114">
         <v>3.2133333333333334</v>
       </c>
+      <c r="C114">
+        <v>0</v>
+      </c>
+      <c r="D114">
+        <v>0</v>
+      </c>
+      <c r="E114">
+        <v>0</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
@@ -65779,6 +66619,15 @@
       <c r="B115">
         <v>3.223333333333333</v>
       </c>
+      <c r="C115">
+        <v>0</v>
+      </c>
+      <c r="D115">
+        <v>0</v>
+      </c>
+      <c r="E115">
+        <v>0</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
@@ -65787,6 +66636,15 @@
       <c r="B116">
         <v>3.243333333333333</v>
       </c>
+      <c r="C116">
+        <v>0</v>
+      </c>
+      <c r="D116">
+        <v>0</v>
+      </c>
+      <c r="E116">
+        <v>0</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
@@ -65795,6 +66653,15 @@
       <c r="B117">
         <v>3.19</v>
       </c>
+      <c r="C117">
+        <v>0</v>
+      </c>
+      <c r="D117">
+        <v>0</v>
+      </c>
+      <c r="E117">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
@@ -65803,6 +66670,15 @@
       <c r="B118">
         <v>3.52</v>
       </c>
+      <c r="C118">
+        <v>0</v>
+      </c>
+      <c r="D118">
+        <v>0</v>
+      </c>
+      <c r="E118">
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
@@ -65811,6 +66687,15 @@
       <c r="B119">
         <v>3.8433333333333333</v>
       </c>
+      <c r="C119">
+        <v>0</v>
+      </c>
+      <c r="D119">
+        <v>0</v>
+      </c>
+      <c r="E119">
+        <v>0</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
@@ -65819,6 +66704,15 @@
       <c r="B120">
         <v>3.756666666666667</v>
       </c>
+      <c r="C120">
+        <v>0</v>
+      </c>
+      <c r="D120">
+        <v>0</v>
+      </c>
+      <c r="E120">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
@@ -65827,6 +66721,15 @@
       <c r="B121">
         <v>3.8033333333333332</v>
       </c>
+      <c r="C121">
+        <v>0</v>
+      </c>
+      <c r="D121">
+        <v>0</v>
+      </c>
+      <c r="E121">
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
@@ -65835,6 +66738,15 @@
       <c r="B122">
         <v>3.7933333333333334</v>
       </c>
+      <c r="C122">
+        <v>0</v>
+      </c>
+      <c r="D122">
+        <v>0</v>
+      </c>
+      <c r="E122">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
@@ -65843,6 +66755,15 @@
       <c r="B123">
         <v>3.82</v>
       </c>
+      <c r="C123">
+        <v>0</v>
+      </c>
+      <c r="D123">
+        <v>0</v>
+      </c>
+      <c r="E123">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
@@ -65851,6 +66772,15 @@
       <c r="B124">
         <v>3.816666666666667</v>
       </c>
+      <c r="C124">
+        <v>0</v>
+      </c>
+      <c r="D124">
+        <v>0</v>
+      </c>
+      <c r="E124">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
@@ -65859,6 +66789,15 @@
       <c r="B125">
         <v>3.79</v>
       </c>
+      <c r="C125">
+        <v>0</v>
+      </c>
+      <c r="D125">
+        <v>0</v>
+      </c>
+      <c r="E125">
+        <v>0</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
@@ -65867,6 +66806,15 @@
       <c r="B126">
         <v>3.7533333333333334</v>
       </c>
+      <c r="C126">
+        <v>0</v>
+      </c>
+      <c r="D126">
+        <v>0</v>
+      </c>
+      <c r="E126">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
@@ -65875,6 +66823,15 @@
       <c r="B127">
         <v>3.85</v>
       </c>
+      <c r="C127">
+        <v>0</v>
+      </c>
+      <c r="D127">
+        <v>0</v>
+      </c>
+      <c r="E127">
+        <v>0</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
@@ -65883,6 +66840,15 @@
       <c r="B128">
         <v>3.9133333333333336</v>
       </c>
+      <c r="C128">
+        <v>0</v>
+      </c>
+      <c r="D128">
+        <v>0</v>
+      </c>
+      <c r="E128">
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
@@ -65891,6 +66857,15 @@
       <c r="B129">
         <v>3.89</v>
       </c>
+      <c r="C129">
+        <v>0</v>
+      </c>
+      <c r="D129">
+        <v>0</v>
+      </c>
+      <c r="E129">
+        <v>0</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
@@ -65899,6 +66874,15 @@
       <c r="B130">
         <v>3.97</v>
       </c>
+      <c r="C130">
+        <v>0</v>
+      </c>
+      <c r="D130">
+        <v>0</v>
+      </c>
+      <c r="E130">
+        <v>0</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
@@ -65907,6 +66891,15 @@
       <c r="B131">
         <v>4.006666666666667</v>
       </c>
+      <c r="C131">
+        <v>0</v>
+      </c>
+      <c r="D131">
+        <v>0</v>
+      </c>
+      <c r="E131">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
@@ -65915,6 +66908,15 @@
       <c r="B132">
         <v>3.95</v>
       </c>
+      <c r="C132">
+        <v>0</v>
+      </c>
+      <c r="D132">
+        <v>0</v>
+      </c>
+      <c r="E132">
+        <v>0</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
@@ -65923,6 +66925,15 @@
       <c r="B133">
         <v>3.9633333333333334</v>
       </c>
+      <c r="C133">
+        <v>0</v>
+      </c>
+      <c r="D133">
+        <v>0</v>
+      </c>
+      <c r="E133">
+        <v>0</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
@@ -65931,6 +66942,15 @@
       <c r="B134">
         <v>3.96</v>
       </c>
+      <c r="C134">
+        <v>0</v>
+      </c>
+      <c r="D134">
+        <v>0</v>
+      </c>
+      <c r="E134">
+        <v>0</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
@@ -65939,6 +66959,15 @@
       <c r="B135">
         <v>3.9833333333333334</v>
       </c>
+      <c r="C135">
+        <v>0</v>
+      </c>
+      <c r="D135">
+        <v>0</v>
+      </c>
+      <c r="E135">
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
@@ -65947,6 +66976,15 @@
       <c r="B136">
         <v>3.6266666666666665</v>
       </c>
+      <c r="C136">
+        <v>0</v>
+      </c>
+      <c r="D136">
+        <v>0</v>
+      </c>
+      <c r="E136">
+        <v>0</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
@@ -65955,6 +66993,15 @@
       <c r="B137">
         <v>4.006666666666667</v>
       </c>
+      <c r="C137">
+        <v>0</v>
+      </c>
+      <c r="D137">
+        <v>0</v>
+      </c>
+      <c r="E137">
+        <v>0</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
@@ -65963,6 +67010,15 @@
       <c r="B138">
         <v>3.953333333333333</v>
       </c>
+      <c r="C138">
+        <v>0</v>
+      </c>
+      <c r="D138">
+        <v>0</v>
+      </c>
+      <c r="E138">
+        <v>0</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
@@ -65971,6 +67027,15 @@
       <c r="B139">
         <v>4.036666666666667</v>
       </c>
+      <c r="C139">
+        <v>0</v>
+      </c>
+      <c r="D139">
+        <v>0</v>
+      </c>
+      <c r="E139">
+        <v>0</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
@@ -65979,6 +67044,15 @@
       <c r="B140">
         <v>3.95</v>
       </c>
+      <c r="C140">
+        <v>0</v>
+      </c>
+      <c r="D140">
+        <v>0</v>
+      </c>
+      <c r="E140">
+        <v>0</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
@@ -65987,6 +67061,15 @@
       <c r="B141">
         <v>4.016666666666667</v>
       </c>
+      <c r="C141">
+        <v>0</v>
+      </c>
+      <c r="D141">
+        <v>0</v>
+      </c>
+      <c r="E141">
+        <v>0</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
@@ -65995,6 +67078,15 @@
       <c r="B142">
         <v>4.046666666666667</v>
       </c>
+      <c r="C142">
+        <v>0</v>
+      </c>
+      <c r="D142">
+        <v>0</v>
+      </c>
+      <c r="E142">
+        <v>0</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
@@ -66003,6 +67095,15 @@
       <c r="B143">
         <v>4.076666666666667</v>
       </c>
+      <c r="C143">
+        <v>0</v>
+      </c>
+      <c r="D143">
+        <v>0</v>
+      </c>
+      <c r="E143">
+        <v>0</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
@@ -66011,6 +67112,15 @@
       <c r="B144">
         <v>4.03</v>
       </c>
+      <c r="C144">
+        <v>0</v>
+      </c>
+      <c r="D144">
+        <v>0</v>
+      </c>
+      <c r="E144">
+        <v>0</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
@@ -66019,6 +67129,15 @@
       <c r="B145">
         <v>4.05</v>
       </c>
+      <c r="C145">
+        <v>0</v>
+      </c>
+      <c r="D145">
+        <v>0</v>
+      </c>
+      <c r="E145">
+        <v>0</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
@@ -66027,6 +67146,15 @@
       <c r="B146">
         <v>4.236666666666666</v>
       </c>
+      <c r="C146">
+        <v>0</v>
+      </c>
+      <c r="D146">
+        <v>0</v>
+      </c>
+      <c r="E146">
+        <v>0</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
@@ -66035,6 +67163,15 @@
       <c r="B147">
         <v>4.16</v>
       </c>
+      <c r="C147">
+        <v>0</v>
+      </c>
+      <c r="D147">
+        <v>0</v>
+      </c>
+      <c r="E147">
+        <v>0</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
@@ -66043,6 +67180,15 @@
       <c r="B148">
         <v>4.04</v>
       </c>
+      <c r="C148">
+        <v>0</v>
+      </c>
+      <c r="D148">
+        <v>0</v>
+      </c>
+      <c r="E148">
+        <v>0</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
@@ -66051,6 +67197,15 @@
       <c r="B149">
         <v>3.5166666666666666</v>
       </c>
+      <c r="C149">
+        <v>0</v>
+      </c>
+      <c r="D149">
+        <v>0</v>
+      </c>
+      <c r="E149">
+        <v>0</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
@@ -66059,6 +67214,15 @@
       <c r="B150">
         <v>3.54</v>
       </c>
+      <c r="C150">
+        <v>0</v>
+      </c>
+      <c r="D150">
+        <v>0</v>
+      </c>
+      <c r="E150">
+        <v>0</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
@@ -66067,6 +67231,15 @@
       <c r="B151">
         <v>4.0633333333333335</v>
       </c>
+      <c r="C151">
+        <v>0</v>
+      </c>
+      <c r="D151">
+        <v>0</v>
+      </c>
+      <c r="E151">
+        <v>0</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
@@ -66075,6 +67248,15 @@
       <c r="B152">
         <v>4.07</v>
       </c>
+      <c r="C152">
+        <v>0</v>
+      </c>
+      <c r="D152">
+        <v>0</v>
+      </c>
+      <c r="E152">
+        <v>0</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
@@ -66083,6 +67265,15 @@
       <c r="B153">
         <v>4.153333333333333</v>
       </c>
+      <c r="C153">
+        <v>0</v>
+      </c>
+      <c r="D153">
+        <v>0</v>
+      </c>
+      <c r="E153">
+        <v>0</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
@@ -66091,6 +67282,15 @@
       <c r="B154">
         <v>4.076666666666667</v>
       </c>
+      <c r="C154">
+        <v>0</v>
+      </c>
+      <c r="D154">
+        <v>0</v>
+      </c>
+      <c r="E154">
+        <v>0</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
@@ -66099,6 +67299,15 @@
       <c r="B155">
         <v>4.036666666666667</v>
       </c>
+      <c r="C155">
+        <v>0</v>
+      </c>
+      <c r="D155">
+        <v>0</v>
+      </c>
+      <c r="E155">
+        <v>0</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
@@ -66107,6 +67316,15 @@
       <c r="B156">
         <v>3.4</v>
       </c>
+      <c r="C156">
+        <v>0</v>
+      </c>
+      <c r="D156">
+        <v>0</v>
+      </c>
+      <c r="E156">
+        <v>0</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
@@ -66115,6 +67333,15 @@
       <c r="B157">
         <v>3.42</v>
       </c>
+      <c r="C157">
+        <v>0</v>
+      </c>
+      <c r="D157">
+        <v>0</v>
+      </c>
+      <c r="E157">
+        <v>0</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
@@ -66123,6 +67350,15 @@
       <c r="B158">
         <v>3.3766666666666665</v>
       </c>
+      <c r="C158">
+        <v>0</v>
+      </c>
+      <c r="D158">
+        <v>0</v>
+      </c>
+      <c r="E158">
+        <v>0</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
@@ -66131,6 +67367,15 @@
       <c r="B159">
         <v>3.3066666666666666</v>
       </c>
+      <c r="C159">
+        <v>0</v>
+      </c>
+      <c r="D159">
+        <v>0</v>
+      </c>
+      <c r="E159">
+        <v>0</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
@@ -66139,6 +67384,15 @@
       <c r="B160">
         <v>3.3366666666666664</v>
       </c>
+      <c r="C160">
+        <v>0</v>
+      </c>
+      <c r="D160">
+        <v>0</v>
+      </c>
+      <c r="E160">
+        <v>0</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
@@ -66147,6 +67401,15 @@
       <c r="B161">
         <v>3.3766666666666665</v>
       </c>
+      <c r="C161">
+        <v>0</v>
+      </c>
+      <c r="D161">
+        <v>0</v>
+      </c>
+      <c r="E161">
+        <v>0</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
@@ -66155,6 +67418,15 @@
       <c r="B162">
         <v>3.46</v>
       </c>
+      <c r="C162">
+        <v>0</v>
+      </c>
+      <c r="D162">
+        <v>0</v>
+      </c>
+      <c r="E162">
+        <v>0</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
@@ -66163,6 +67435,15 @@
       <c r="B163">
         <v>3.4033333333333333</v>
       </c>
+      <c r="C163">
+        <v>0</v>
+      </c>
+      <c r="D163">
+        <v>0</v>
+      </c>
+      <c r="E163">
+        <v>0</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
@@ -66171,6 +67452,15 @@
       <c r="B164">
         <v>3.4466666666666668</v>
       </c>
+      <c r="C164">
+        <v>0</v>
+      </c>
+      <c r="D164">
+        <v>0</v>
+      </c>
+      <c r="E164">
+        <v>0</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="s">
@@ -66179,6 +67469,15 @@
       <c r="B165">
         <v>3.6666666666666665</v>
       </c>
+      <c r="C165">
+        <v>0</v>
+      </c>
+      <c r="D165">
+        <v>0</v>
+      </c>
+      <c r="E165">
+        <v>0</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
@@ -66187,6 +67486,15 @@
       <c r="B166">
         <v>3.3333333333333335</v>
       </c>
+      <c r="C166">
+        <v>0</v>
+      </c>
+      <c r="D166">
+        <v>0</v>
+      </c>
+      <c r="E166">
+        <v>0</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="s">
@@ -66195,6 +67503,15 @@
       <c r="B167">
         <v>3.3233333333333333</v>
       </c>
+      <c r="C167">
+        <v>0</v>
+      </c>
+      <c r="D167">
+        <v>0</v>
+      </c>
+      <c r="E167">
+        <v>0</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
@@ -66203,6 +67520,15 @@
       <c r="B168">
         <v>3.296666666666667</v>
       </c>
+      <c r="C168">
+        <v>0</v>
+      </c>
+      <c r="D168">
+        <v>0</v>
+      </c>
+      <c r="E168">
+        <v>0</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
@@ -66211,6 +67537,15 @@
       <c r="B169">
         <v>3.9633333333333334</v>
       </c>
+      <c r="C169">
+        <v>0</v>
+      </c>
+      <c r="D169">
+        <v>0</v>
+      </c>
+      <c r="E169">
+        <v>0</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
@@ -66219,6 +67554,15 @@
       <c r="B170">
         <v>4.023333333333333</v>
       </c>
+      <c r="C170">
+        <v>0</v>
+      </c>
+      <c r="D170">
+        <v>0</v>
+      </c>
+      <c r="E170">
+        <v>0</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
@@ -66227,6 +67571,15 @@
       <c r="B171">
         <v>3.9633333333333334</v>
       </c>
+      <c r="C171">
+        <v>0</v>
+      </c>
+      <c r="D171">
+        <v>0</v>
+      </c>
+      <c r="E171">
+        <v>0</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
@@ -66235,6 +67588,15 @@
       <c r="B172">
         <v>3.8766666666666665</v>
       </c>
+      <c r="C172">
+        <v>0</v>
+      </c>
+      <c r="D172">
+        <v>0</v>
+      </c>
+      <c r="E172">
+        <v>0</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
@@ -66243,6 +67605,15 @@
       <c r="B173">
         <v>4.05</v>
       </c>
+      <c r="C173">
+        <v>0</v>
+      </c>
+      <c r="D173">
+        <v>0</v>
+      </c>
+      <c r="E173">
+        <v>0</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
@@ -66251,6 +67622,15 @@
       <c r="B174">
         <v>4.033333333333333</v>
       </c>
+      <c r="C174">
+        <v>0</v>
+      </c>
+      <c r="D174">
+        <v>0</v>
+      </c>
+      <c r="E174">
+        <v>0</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
@@ -66259,6 +67639,15 @@
       <c r="B175">
         <v>3.9966666666666666</v>
       </c>
+      <c r="C175">
+        <v>0</v>
+      </c>
+      <c r="D175">
+        <v>0</v>
+      </c>
+      <c r="E175">
+        <v>0</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="s">
@@ -66267,6 +67656,15 @@
       <c r="B176">
         <v>4.056666666666667</v>
       </c>
+      <c r="C176">
+        <v>0</v>
+      </c>
+      <c r="D176">
+        <v>0</v>
+      </c>
+      <c r="E176">
+        <v>0</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="s">
@@ -66275,6 +67673,15 @@
       <c r="B177">
         <v>4.003333333333333</v>
       </c>
+      <c r="C177">
+        <v>0</v>
+      </c>
+      <c r="D177">
+        <v>0</v>
+      </c>
+      <c r="E177">
+        <v>0</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
@@ -66283,6 +67690,15 @@
       <c r="B178">
         <v>3.973333333333333</v>
       </c>
+      <c r="C178">
+        <v>0</v>
+      </c>
+      <c r="D178">
+        <v>0</v>
+      </c>
+      <c r="E178">
+        <v>0</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
@@ -66291,6 +67707,15 @@
       <c r="B179">
         <v>3.9966666666666666</v>
       </c>
+      <c r="C179">
+        <v>0</v>
+      </c>
+      <c r="D179">
+        <v>0</v>
+      </c>
+      <c r="E179">
+        <v>0</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="s">
@@ -66299,6 +67724,15 @@
       <c r="B180">
         <v>4.04</v>
       </c>
+      <c r="C180">
+        <v>0</v>
+      </c>
+      <c r="D180">
+        <v>0</v>
+      </c>
+      <c r="E180">
+        <v>0</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="s">
@@ -66307,6 +67741,15 @@
       <c r="B181">
         <v>4.156666666666666</v>
       </c>
+      <c r="C181">
+        <v>0</v>
+      </c>
+      <c r="D181">
+        <v>0</v>
+      </c>
+      <c r="E181">
+        <v>0</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="s">
@@ -66315,6 +67758,15 @@
       <c r="B182">
         <v>4.053333333333334</v>
       </c>
+      <c r="C182">
+        <v>0</v>
+      </c>
+      <c r="D182">
+        <v>0</v>
+      </c>
+      <c r="E182">
+        <v>0</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="s">
@@ -66323,6 +67775,15 @@
       <c r="B183">
         <v>4.066666666666666</v>
       </c>
+      <c r="C183">
+        <v>0</v>
+      </c>
+      <c r="D183">
+        <v>0</v>
+      </c>
+      <c r="E183">
+        <v>0</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="s">
@@ -66331,6 +67792,15 @@
       <c r="B184">
         <v>4.013333333333334</v>
       </c>
+      <c r="C184">
+        <v>0</v>
+      </c>
+      <c r="D184">
+        <v>0</v>
+      </c>
+      <c r="E184">
+        <v>0</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="s">
@@ -66339,6 +67809,15 @@
       <c r="B185">
         <v>4.133333333333334</v>
       </c>
+      <c r="C185">
+        <v>0</v>
+      </c>
+      <c r="D185">
+        <v>0</v>
+      </c>
+      <c r="E185">
+        <v>0</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="s">
@@ -66347,6 +67826,15 @@
       <c r="B186">
         <v>4.003333333333333</v>
       </c>
+      <c r="C186">
+        <v>0</v>
+      </c>
+      <c r="D186">
+        <v>0</v>
+      </c>
+      <c r="E186">
+        <v>0</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="s">
@@ -66355,6 +67843,15 @@
       <c r="B187">
         <v>4.126666666666667</v>
       </c>
+      <c r="C187">
+        <v>0</v>
+      </c>
+      <c r="D187">
+        <v>0</v>
+      </c>
+      <c r="E187">
+        <v>0</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="s">
@@ -66363,6 +67860,15 @@
       <c r="B188">
         <v>4.1033333333333335</v>
       </c>
+      <c r="C188">
+        <v>0</v>
+      </c>
+      <c r="D188">
+        <v>0</v>
+      </c>
+      <c r="E188">
+        <v>0</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="s">
@@ -66371,6 +67877,15 @@
       <c r="B189">
         <v>4.066666666666666</v>
       </c>
+      <c r="C189">
+        <v>0</v>
+      </c>
+      <c r="D189">
+        <v>0</v>
+      </c>
+      <c r="E189">
+        <v>0</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="s">
@@ -66379,6 +67894,15 @@
       <c r="B190">
         <v>4.05</v>
       </c>
+      <c r="C190">
+        <v>0</v>
+      </c>
+      <c r="D190">
+        <v>0</v>
+      </c>
+      <c r="E190">
+        <v>0</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="s">
@@ -66387,6 +67911,15 @@
       <c r="B191">
         <v>4.15</v>
       </c>
+      <c r="C191">
+        <v>0</v>
+      </c>
+      <c r="D191">
+        <v>0</v>
+      </c>
+      <c r="E191">
+        <v>0</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
@@ -66395,6 +67928,15 @@
       <c r="B192">
         <v>4.09</v>
       </c>
+      <c r="C192">
+        <v>0</v>
+      </c>
+      <c r="D192">
+        <v>0</v>
+      </c>
+      <c r="E192">
+        <v>0</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="s">
@@ -66403,6 +67945,15 @@
       <c r="B193">
         <v>4.253333333333333</v>
       </c>
+      <c r="C193">
+        <v>0</v>
+      </c>
+      <c r="D193">
+        <v>0</v>
+      </c>
+      <c r="E193">
+        <v>0</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="s">
@@ -66411,6 +67962,15 @@
       <c r="B194">
         <v>4.1866666666666665</v>
       </c>
+      <c r="C194">
+        <v>0</v>
+      </c>
+      <c r="D194">
+        <v>0</v>
+      </c>
+      <c r="E194">
+        <v>0</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="s">
@@ -66419,6 +67979,15 @@
       <c r="B195">
         <v>4.14</v>
       </c>
+      <c r="C195">
+        <v>0</v>
+      </c>
+      <c r="D195">
+        <v>0</v>
+      </c>
+      <c r="E195">
+        <v>0</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="s">
@@ -66427,6 +67996,15 @@
       <c r="B196">
         <v>4.07</v>
       </c>
+      <c r="C196">
+        <v>0</v>
+      </c>
+      <c r="D196">
+        <v>0</v>
+      </c>
+      <c r="E196">
+        <v>0</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="s">
@@ -66435,6 +68013,15 @@
       <c r="B197">
         <v>4.0633333333333335</v>
       </c>
+      <c r="C197">
+        <v>0</v>
+      </c>
+      <c r="D197">
+        <v>0</v>
+      </c>
+      <c r="E197">
+        <v>0</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="s">
@@ -66443,6 +68030,15 @@
       <c r="B198">
         <v>3.993333333333333</v>
       </c>
+      <c r="C198">
+        <v>0</v>
+      </c>
+      <c r="D198">
+        <v>0</v>
+      </c>
+      <c r="E198">
+        <v>0</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="s">
@@ -66451,6 +68047,15 @@
       <c r="B199">
         <v>4.016666666666667</v>
       </c>
+      <c r="C199">
+        <v>0</v>
+      </c>
+      <c r="D199">
+        <v>0</v>
+      </c>
+      <c r="E199">
+        <v>0</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="s">
@@ -66459,6 +68064,15 @@
       <c r="B200">
         <v>4.056666666666667</v>
       </c>
+      <c r="C200">
+        <v>0</v>
+      </c>
+      <c r="D200">
+        <v>0</v>
+      </c>
+      <c r="E200">
+        <v>0</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="s">
@@ -66467,6 +68081,15 @@
       <c r="B201">
         <v>4.16</v>
       </c>
+      <c r="C201">
+        <v>0</v>
+      </c>
+      <c r="D201">
+        <v>0</v>
+      </c>
+      <c r="E201">
+        <v>0</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="s">
@@ -66475,6 +68098,15 @@
       <c r="B202">
         <v>4.12</v>
       </c>
+      <c r="C202">
+        <v>0</v>
+      </c>
+      <c r="D202">
+        <v>0</v>
+      </c>
+      <c r="E202">
+        <v>0</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="s">
@@ -66483,6 +68115,15 @@
       <c r="B203">
         <v>4.01</v>
       </c>
+      <c r="C203">
+        <v>0</v>
+      </c>
+      <c r="D203">
+        <v>0</v>
+      </c>
+      <c r="E203">
+        <v>0</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="s">
@@ -66491,6 +68132,15 @@
       <c r="B204">
         <v>4.053333333333334</v>
       </c>
+      <c r="C204">
+        <v>0</v>
+      </c>
+      <c r="D204">
+        <v>0</v>
+      </c>
+      <c r="E204">
+        <v>0</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="s">
@@ -66499,6 +68149,15 @@
       <c r="B205">
         <v>4.056666666666667</v>
       </c>
+      <c r="C205">
+        <v>0</v>
+      </c>
+      <c r="D205">
+        <v>0</v>
+      </c>
+      <c r="E205">
+        <v>0</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="s">
@@ -66507,6 +68166,15 @@
       <c r="B206">
         <v>4.036666666666667</v>
       </c>
+      <c r="C206">
+        <v>0</v>
+      </c>
+      <c r="D206">
+        <v>0</v>
+      </c>
+      <c r="E206">
+        <v>0</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="s">
@@ -66515,6 +68183,15 @@
       <c r="B207">
         <v>3.97</v>
       </c>
+      <c r="C207">
+        <v>0</v>
+      </c>
+      <c r="D207">
+        <v>0</v>
+      </c>
+      <c r="E207">
+        <v>0</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="s">
@@ -66523,6 +68200,15 @@
       <c r="B208">
         <v>4.046666666666667</v>
       </c>
+      <c r="C208">
+        <v>0</v>
+      </c>
+      <c r="D208">
+        <v>0</v>
+      </c>
+      <c r="E208">
+        <v>0</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="s">
@@ -66531,6 +68217,15 @@
       <c r="B209">
         <v>4.13</v>
       </c>
+      <c r="C209">
+        <v>0</v>
+      </c>
+      <c r="D209">
+        <v>0</v>
+      </c>
+      <c r="E209">
+        <v>0</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="s">
@@ -66539,6 +68234,15 @@
       <c r="B210">
         <v>4.073333333333333</v>
       </c>
+      <c r="C210">
+        <v>0</v>
+      </c>
+      <c r="D210">
+        <v>0</v>
+      </c>
+      <c r="E210">
+        <v>0</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="s">
@@ -66547,6 +68251,15 @@
       <c r="B211">
         <v>3.9966666666666666</v>
       </c>
+      <c r="C211">
+        <v>0</v>
+      </c>
+      <c r="D211">
+        <v>0</v>
+      </c>
+      <c r="E211">
+        <v>0</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="s">
@@ -66555,6 +68268,15 @@
       <c r="B212">
         <v>4.1066666666666665</v>
       </c>
+      <c r="C212">
+        <v>0</v>
+      </c>
+      <c r="D212">
+        <v>0</v>
+      </c>
+      <c r="E212">
+        <v>0</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="s">
@@ -66563,6 +68285,15 @@
       <c r="B213">
         <v>4.12</v>
       </c>
+      <c r="C213">
+        <v>0</v>
+      </c>
+      <c r="D213">
+        <v>0</v>
+      </c>
+      <c r="E213">
+        <v>0</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="s">
@@ -66571,6 +68302,15 @@
       <c r="B214">
         <v>4.07</v>
       </c>
+      <c r="C214">
+        <v>0</v>
+      </c>
+      <c r="D214">
+        <v>0</v>
+      </c>
+      <c r="E214">
+        <v>0</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="s">
@@ -66579,6 +68319,15 @@
       <c r="B215">
         <v>4.16</v>
       </c>
+      <c r="C215">
+        <v>0</v>
+      </c>
+      <c r="D215">
+        <v>0</v>
+      </c>
+      <c r="E215">
+        <v>0</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="s">
@@ -66587,6 +68336,15 @@
       <c r="B216">
         <v>4.153333333333333</v>
       </c>
+      <c r="C216">
+        <v>0</v>
+      </c>
+      <c r="D216">
+        <v>0</v>
+      </c>
+      <c r="E216">
+        <v>0</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="s">
@@ -66595,6 +68353,15 @@
       <c r="B217">
         <v>4.136666666666667</v>
       </c>
+      <c r="C217">
+        <v>0</v>
+      </c>
+      <c r="D217">
+        <v>0</v>
+      </c>
+      <c r="E217">
+        <v>0</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="s">
@@ -66603,6 +68370,15 @@
       <c r="B218">
         <v>4.023333333333333</v>
       </c>
+      <c r="C218">
+        <v>0</v>
+      </c>
+      <c r="D218">
+        <v>0</v>
+      </c>
+      <c r="E218">
+        <v>0</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="s">
@@ -66611,6 +68387,15 @@
       <c r="B219">
         <v>4.016666666666667</v>
       </c>
+      <c r="C219">
+        <v>0</v>
+      </c>
+      <c r="D219">
+        <v>0</v>
+      </c>
+      <c r="E219">
+        <v>0</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="s">
@@ -66619,6 +68404,15 @@
       <c r="B220">
         <v>4.05</v>
       </c>
+      <c r="C220">
+        <v>0</v>
+      </c>
+      <c r="D220">
+        <v>0</v>
+      </c>
+      <c r="E220">
+        <v>0</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="s">
@@ -66627,6 +68421,15 @@
       <c r="B221">
         <v>4.1033333333333335</v>
       </c>
+      <c r="C221">
+        <v>0</v>
+      </c>
+      <c r="D221">
+        <v>0</v>
+      </c>
+      <c r="E221">
+        <v>0</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="s">
@@ -66635,6 +68438,15 @@
       <c r="B222">
         <v>4.013333333333334</v>
       </c>
+      <c r="C222">
+        <v>0</v>
+      </c>
+      <c r="D222">
+        <v>0</v>
+      </c>
+      <c r="E222">
+        <v>0</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="s">
@@ -66643,6 +68455,15 @@
       <c r="B223">
         <v>4.113333333333333</v>
       </c>
+      <c r="C223">
+        <v>0</v>
+      </c>
+      <c r="D223">
+        <v>0</v>
+      </c>
+      <c r="E223">
+        <v>0</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="s">
@@ -66651,6 +68472,15 @@
       <c r="B224">
         <v>4</v>
       </c>
+      <c r="C224">
+        <v>0</v>
+      </c>
+      <c r="D224">
+        <v>0</v>
+      </c>
+      <c r="E224">
+        <v>0</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="s">
@@ -66659,6 +68489,15 @@
       <c r="B225">
         <v>4.023333333333333</v>
       </c>
+      <c r="C225">
+        <v>0</v>
+      </c>
+      <c r="D225">
+        <v>0</v>
+      </c>
+      <c r="E225">
+        <v>0</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="s">
@@ -66667,6 +68506,15 @@
       <c r="B226">
         <v>4.04</v>
       </c>
+      <c r="C226">
+        <v>0</v>
+      </c>
+      <c r="D226">
+        <v>0</v>
+      </c>
+      <c r="E226">
+        <v>0</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="s">
@@ -66675,6 +68523,15 @@
       <c r="B227">
         <v>4.056666666666667</v>
       </c>
+      <c r="C227">
+        <v>0</v>
+      </c>
+      <c r="D227">
+        <v>0</v>
+      </c>
+      <c r="E227">
+        <v>0</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="s">
@@ -66683,6 +68540,15 @@
       <c r="B228">
         <v>4.163333333333333</v>
       </c>
+      <c r="C228">
+        <v>0</v>
+      </c>
+      <c r="D228">
+        <v>0</v>
+      </c>
+      <c r="E228">
+        <v>0</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="s">
@@ -66690,6 +68556,15 @@
       </c>
       <c r="B229">
         <v>4.06</v>
+      </c>
+      <c r="C229">
+        <v>0</v>
+      </c>
+      <c r="D229">
+        <v>0</v>
+      </c>
+      <c r="E229">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -66742,6 +68617,9 @@
       <c r="B21">
         <v>1238.68359375</v>
       </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
